--- a/estructuras.xlsx
+++ b/estructuras.xlsx
@@ -1,45 +1,224 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pabloviggiano/Desktop/Carpas/Nueva App Dangiola/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650F9704-86CF-5F4C-A2CD-8CAD9B6E5195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83DD9B54-C0FE-7E4B-B4D8-10DB0FFC569C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C287DC9A-1DBF-BF4A-98FF-A82F95D90B38}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23040" windowHeight="8480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Estructuras" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+  <si>
+    <t>C3-L1</t>
+  </si>
+  <si>
+    <t>C3-H1</t>
+  </si>
+  <si>
+    <t>C4-L1</t>
+  </si>
+  <si>
+    <t>C4-H1</t>
+  </si>
+  <si>
+    <t>C5-L1 (NGR)</t>
+  </si>
+  <si>
+    <t>C5-SB1 (NQN)</t>
+  </si>
+  <si>
+    <t>C5-H1</t>
+  </si>
+  <si>
+    <t>C5-D1</t>
+  </si>
+  <si>
+    <t>C5-H3</t>
+  </si>
+  <si>
+    <t>C5-H2</t>
+  </si>
+  <si>
+    <t>C6-H1</t>
+  </si>
+  <si>
+    <t>C6-SB1</t>
+  </si>
+  <si>
+    <t>C8-D1</t>
+  </si>
+  <si>
+    <t>C8-L1</t>
+  </si>
+  <si>
+    <t>C8-T1</t>
+  </si>
+  <si>
+    <t>C8-L2</t>
+  </si>
+  <si>
+    <t>C10-H2</t>
+  </si>
+  <si>
+    <t>C10-L1</t>
+  </si>
+  <si>
+    <t>C10-L2</t>
+  </si>
+  <si>
+    <t>C10-H3</t>
+  </si>
+  <si>
+    <t>C10-H1</t>
+  </si>
+  <si>
+    <t>C10-D2</t>
+  </si>
+  <si>
+    <t>C10-SB1 (NQN)</t>
+  </si>
+  <si>
+    <t>C10-D1</t>
+  </si>
+  <si>
+    <t>C10-L3</t>
+  </si>
+  <si>
+    <t>C10-L4</t>
+  </si>
+  <si>
+    <t>C10-T1</t>
+  </si>
+  <si>
+    <t>C10-SB2 (NQN)</t>
+  </si>
+  <si>
+    <t>C12-D1</t>
+  </si>
+  <si>
+    <t>C12-H2</t>
+  </si>
+  <si>
+    <t>C12-H3</t>
+  </si>
+  <si>
+    <t>C12-H1</t>
+  </si>
+  <si>
+    <t>C12-H4</t>
+  </si>
+  <si>
+    <t>C15-H1</t>
+  </si>
+  <si>
+    <t>C15-T1</t>
+  </si>
+  <si>
+    <t>C20-H3 (CRV-C15)</t>
+  </si>
+  <si>
+    <t>C20-H2</t>
+  </si>
+  <si>
+    <t>C20-T1 (C15)</t>
+  </si>
+  <si>
+    <t>C20-L2</t>
+  </si>
+  <si>
+    <t>C20-SB3 (C15-NQN)</t>
+  </si>
+  <si>
+    <t>C20-SB2 (NGR-C15)</t>
+  </si>
+  <si>
+    <t>C20-H8 (C15)</t>
+  </si>
+  <si>
+    <t>C20-SB1 (NGR)</t>
+  </si>
+  <si>
+    <t>C20-L4 (C15)</t>
+  </si>
+  <si>
+    <t>C20-L3</t>
+  </si>
+  <si>
+    <t>C20-H1</t>
+  </si>
+  <si>
+    <t>C20-H7 (C15)</t>
+  </si>
+  <si>
+    <t>C20-H4 (C15)</t>
+  </si>
+  <si>
+    <t>C20-H6 (C15)</t>
+  </si>
+  <si>
+    <t>C20-H5</t>
+  </si>
+  <si>
+    <t>C20-L1 (C15)</t>
+  </si>
+  <si>
+    <t>C25-D1</t>
+  </si>
+  <si>
+    <t>C30-H3 (LX)</t>
+  </si>
+  <si>
+    <t>C30-H6</t>
+  </si>
+  <si>
+    <t>C30-H4 (LF)</t>
+  </si>
+  <si>
+    <t>C30-H5</t>
+  </si>
+  <si>
+    <t>C30-L4</t>
+  </si>
+  <si>
+    <t>C30-H1 (CRV)</t>
+  </si>
+  <si>
+    <t>C30-H2 (LF)</t>
+  </si>
+  <si>
+    <t>C30-L2</t>
+  </si>
+  <si>
+    <t>C30-H7 (CRV)</t>
+  </si>
+  <si>
+    <t>C30-SB1</t>
+  </si>
+  <si>
+    <t>C30-L1</t>
+  </si>
+  <si>
+    <t>C30-H8</t>
+  </si>
+  <si>
+    <t>C30-L3</t>
+  </si>
+  <si>
+    <t>C40-H1</t>
+  </si>
   <si>
     <t>Modelo_Estructura</t>
   </si>
@@ -47,25 +226,7 @@
     <t>Arcos totales</t>
   </si>
   <si>
-    <t>Estructura</t>
-  </si>
-  <si>
     <t>Frente</t>
-  </si>
-  <si>
-    <t>C10-L3</t>
-  </si>
-  <si>
-    <t>Aluminio</t>
-  </si>
-  <si>
-    <t>C10-L2</t>
-  </si>
-  <si>
-    <t>C10-L1</t>
-  </si>
-  <si>
-    <t>C10-L4</t>
   </si>
   <si>
     <t>Largo_Maximo</t>
@@ -75,63 +236,40 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -139,18 +277,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF666666"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF666666"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF666666"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF666666"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,9 +328,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -179,39 +338,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -263,7 +422,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -315,7 +474,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -374,6 +533,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -382,13 +548,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -453,137 +612,964 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7396CC6D-882D-D245-A222-145BC9E0022D}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="4">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4">
+        <v>55</v>
+      </c>
+      <c r="D2" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B3" s="4">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B4" s="4">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B5" s="4">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4">
+        <v>48</v>
+      </c>
+      <c r="D5" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>68</v>
+      </c>
+      <c r="D8" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="B11" s="4">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4">
+        <v>6</v>
+      </c>
+      <c r="C12" s="4">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4">
+        <v>30</v>
+      </c>
+      <c r="D14" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4">
+        <v>25</v>
+      </c>
+      <c r="D15" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4">
         <v>4</v>
       </c>
-      <c r="B2" s="6">
+    </row>
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4">
+        <v>8</v>
+      </c>
+      <c r="C17" s="4">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>30</v>
+      </c>
+      <c r="D18" s="4">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4">
-        <v>10</v>
-      </c>
-      <c r="E2" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>25</v>
+      </c>
+      <c r="D19" s="4">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
+    </row>
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4">
+        <v>30</v>
+      </c>
+      <c r="D20" s="4">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="4">
-        <v>10</v>
-      </c>
-      <c r="E3" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>15</v>
+      </c>
+      <c r="D21" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4">
+        <v>30</v>
+      </c>
+      <c r="D22" s="4">
         <v>7</v>
       </c>
-      <c r="B4" s="6">
+    </row>
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4">
+        <v>85</v>
+      </c>
+      <c r="D23" s="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4">
+        <v>20</v>
+      </c>
+      <c r="D24" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4">
+        <v>40</v>
+      </c>
+      <c r="D25" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4">
+        <v>10</v>
+      </c>
+      <c r="C26" s="4">
+        <v>30</v>
+      </c>
+      <c r="D26" s="4">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4">
+        <v>30</v>
+      </c>
+      <c r="D27" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4">
+        <v>10</v>
+      </c>
+      <c r="C28" s="4">
+        <v>57</v>
+      </c>
+      <c r="D28" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4">
+        <v>12</v>
+      </c>
+      <c r="C30" s="4">
+        <v>25</v>
+      </c>
+      <c r="D30" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4">
+        <v>12</v>
+      </c>
+      <c r="C31" s="4">
+        <v>20</v>
+      </c>
+      <c r="D31" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4">
+        <v>12</v>
+      </c>
+      <c r="C32" s="4">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4">
+        <v>12</v>
+      </c>
+      <c r="C33" s="4">
+        <v>20</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4">
+        <v>12</v>
+      </c>
+      <c r="C34" s="4">
+        <v>25</v>
+      </c>
+      <c r="D34" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4">
+        <v>15</v>
+      </c>
+      <c r="C35" s="4">
+        <v>20</v>
+      </c>
+      <c r="D35" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4">
+        <v>15</v>
+      </c>
+      <c r="C36" s="4">
+        <v>20</v>
+      </c>
+      <c r="D36" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4">
+        <v>20</v>
+      </c>
+      <c r="C37" s="4">
+        <v>55</v>
+      </c>
+      <c r="D37" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4">
+        <v>20</v>
+      </c>
+      <c r="C38" s="4">
+        <v>35</v>
+      </c>
+      <c r="D38" s="4">
         <v>8</v>
       </c>
-      <c r="B5" s="6">
+    </row>
+    <row r="39" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4">
+        <v>20</v>
+      </c>
+      <c r="C39" s="4">
+        <v>30</v>
+      </c>
+      <c r="D39" s="4">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4">
-        <v>10</v>
-      </c>
-      <c r="E5" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C8" s="4"/>
+    </row>
+    <row r="40" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4">
+        <v>20</v>
+      </c>
+      <c r="C40" s="4">
+        <v>30</v>
+      </c>
+      <c r="D40" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4">
+        <v>20</v>
+      </c>
+      <c r="C41" s="4">
+        <v>50</v>
+      </c>
+      <c r="D41" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4">
+        <v>20</v>
+      </c>
+      <c r="C42" s="4">
+        <v>50</v>
+      </c>
+      <c r="D42" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4">
+        <v>20</v>
+      </c>
+      <c r="C43" s="4">
+        <v>40</v>
+      </c>
+      <c r="D43" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4">
+        <v>20</v>
+      </c>
+      <c r="C44" s="4">
+        <v>40</v>
+      </c>
+      <c r="D44" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4">
+        <v>20</v>
+      </c>
+      <c r="C45" s="4">
+        <v>50</v>
+      </c>
+      <c r="D45" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4">
+        <v>20</v>
+      </c>
+      <c r="C46" s="4">
+        <v>50</v>
+      </c>
+      <c r="D46" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4">
+        <v>20</v>
+      </c>
+      <c r="C47" s="4">
+        <v>90</v>
+      </c>
+      <c r="D47" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4">
+        <v>20</v>
+      </c>
+      <c r="C48" s="4">
+        <v>45</v>
+      </c>
+      <c r="D48" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4">
+        <v>20</v>
+      </c>
+      <c r="C49" s="4">
+        <v>45</v>
+      </c>
+      <c r="D49" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4">
+        <v>20</v>
+      </c>
+      <c r="C50" s="4">
+        <v>40</v>
+      </c>
+      <c r="D50" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4">
+        <v>20</v>
+      </c>
+      <c r="C51" s="4">
+        <v>35</v>
+      </c>
+      <c r="D51" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4">
+        <v>20</v>
+      </c>
+      <c r="C52" s="4">
+        <v>30</v>
+      </c>
+      <c r="D52" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4">
+        <v>25</v>
+      </c>
+      <c r="C53" s="4">
+        <v>60</v>
+      </c>
+      <c r="D53" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4">
+        <v>30</v>
+      </c>
+      <c r="C54" s="4">
+        <v>100</v>
+      </c>
+      <c r="D54" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4">
+        <v>30</v>
+      </c>
+      <c r="C55" s="4">
+        <v>80</v>
+      </c>
+      <c r="D55" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4">
+        <v>30</v>
+      </c>
+      <c r="C56" s="4">
+        <v>80</v>
+      </c>
+      <c r="D56" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4">
+        <v>30</v>
+      </c>
+      <c r="C57" s="4">
+        <v>55</v>
+      </c>
+      <c r="D57" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="4">
+        <v>30</v>
+      </c>
+      <c r="C58" s="4">
+        <v>80</v>
+      </c>
+      <c r="D58" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="4">
+        <v>30</v>
+      </c>
+      <c r="C59" s="4">
+        <v>60</v>
+      </c>
+      <c r="D59" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="4">
+        <v>30</v>
+      </c>
+      <c r="C60" s="4">
+        <v>20</v>
+      </c>
+      <c r="D60" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="4">
+        <v>30</v>
+      </c>
+      <c r="C61" s="4">
+        <v>40</v>
+      </c>
+      <c r="D61" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="4">
+        <v>30</v>
+      </c>
+      <c r="C62" s="4">
+        <v>80</v>
+      </c>
+      <c r="D62" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="4">
+        <v>30</v>
+      </c>
+      <c r="C63" s="4">
+        <v>30</v>
+      </c>
+      <c r="D63" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="4">
+        <v>30</v>
+      </c>
+      <c r="C64" s="4">
+        <v>50</v>
+      </c>
+      <c r="D64" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="4">
+        <v>30</v>
+      </c>
+      <c r="C65" s="4">
+        <v>50</v>
+      </c>
+      <c r="D65" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="4">
+        <v>30</v>
+      </c>
+      <c r="C66" s="4">
+        <v>80</v>
+      </c>
+      <c r="D66" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="4">
+        <v>40</v>
+      </c>
+      <c r="C67" s="4">
+        <v>70</v>
+      </c>
+      <c r="D67" s="4">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
